--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00929-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00929-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ACF1D11-B8C3-447B-94BB-E2A2841B0416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{328C806C-2090-49DE-8FD4-239F9EE13FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{13333C41-7294-428D-8599-062E4A5B8976}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{7BC6F668-D305-4342-A06B-BF22E68AC213}"/>
   </bookViews>
   <sheets>
     <sheet name="00929-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1651,20 +1651,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A7617BB-44C1-4902-906E-7C756C611CB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BD2C5D1-2AAB-491A-A21B-67C7DB73AD2F}">
   <dimension ref="A1:R42"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1692,7 +1692,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1722,7 +1722,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1818,7 +1818,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1898,7 +1898,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2025</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2024</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>9.15</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>26</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>26</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>26</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>26</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>26</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="49">
         <v>2023</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
         <v>26</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>26</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>26</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>26</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>26</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>26</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="51" t="s">
         <v>88</v>
       </c>
